--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.44488</v>
+        <v>17.20302</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30385</v>
+        <v>16.55907</v>
       </c>
       <c r="E2" t="n">
-        <v>16.57155</v>
+        <v>16.69932</v>
       </c>
       <c r="F2" t="n">
-        <v>41.5183</v>
+        <v>41.7633</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04996</v>
+        <v>0.05147</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79969</v>
+        <v>1.8211</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.60002</v>
+        <v>16.82867</v>
       </c>
       <c r="D3" t="n">
-        <v>16.25305</v>
+        <v>16.53389</v>
       </c>
       <c r="E3" t="n">
-        <v>16.30257</v>
+        <v>16.72881</v>
       </c>
       <c r="F3" t="n">
-        <v>43.2602</v>
+        <v>41.75359</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04969</v>
+        <v>0.05116</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8541</v>
+        <v>1.82906</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.57678</v>
+        <v>16.66308</v>
       </c>
       <c r="D4" t="n">
-        <v>16.5327</v>
+        <v>16.47451</v>
       </c>
       <c r="E4" t="n">
-        <v>16.93443</v>
+        <v>16.58315</v>
       </c>
       <c r="F4" t="n">
-        <v>42.39867</v>
+        <v>41.99588</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05014</v>
+        <v>0.05083</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81932</v>
+        <v>1.79144</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.89004</v>
+        <v>16.40701</v>
       </c>
       <c r="D6" t="n">
-        <v>16.0808</v>
+        <v>15.64077</v>
       </c>
       <c r="E6" t="n">
-        <v>16.35936</v>
+        <v>16.28279</v>
       </c>
       <c r="F6" t="n">
-        <v>22.06184</v>
+        <v>21.70539</v>
       </c>
       <c r="G6" t="n">
-        <v>33.9808</v>
+        <v>33.36833</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.55555</v>
+        <v>16.5651</v>
       </c>
       <c r="D7" t="n">
-        <v>16.26796</v>
+        <v>16.1701</v>
       </c>
       <c r="E7" t="n">
-        <v>16.24413</v>
+        <v>16.39616</v>
       </c>
       <c r="F7" t="n">
-        <v>22.19097</v>
+        <v>21.83113</v>
       </c>
       <c r="G7" t="n">
-        <v>33.32702</v>
+        <v>34.05033</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.98652</v>
+        <v>16.8993</v>
       </c>
       <c r="D8" t="n">
-        <v>15.55071</v>
+        <v>16.2661</v>
       </c>
       <c r="E8" t="n">
-        <v>16.41781</v>
+        <v>16.35558</v>
       </c>
       <c r="F8" t="n">
-        <v>21.97459</v>
+        <v>21.46235</v>
       </c>
       <c r="G8" t="n">
-        <v>33.69523</v>
+        <v>34.58643</v>
       </c>
     </row>
   </sheetData>
